--- a/tests/test_extract/testing_files/base_source_export.xlsx
+++ b/tests/test_extract/testing_files/base_source_export.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sparda\Desktop\Moseley Lab\Code\MESSES\tests\test_extract\testing_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sparda\Desktop\Moseley Lab\Code\MESSES_main\MESSES\tests\test_extract\testing_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451AC236-11F1-46BB-91A5-09B2C891205E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16E65FD-2D9E-44A3-B857-F727185A0E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4335" yWindow="1515" windowWidth="21720" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="3975" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="#export" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -25,245 +25,245 @@
     <t>#tags</t>
   </si>
   <si>
+    <t>#ignore</t>
+  </si>
+  <si>
+    <t>#measurement.id</t>
+  </si>
+  <si>
+    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd-13C0-01_A0_Colon_T03-2017_naive_170427_UKy_GCB_rep1-quench</t>
+  </si>
+  <si>
+    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd-13C1-01_A0_Colon_T03-2017_naive_170427_UKy_GCB_rep1-quench</t>
+  </si>
+  <si>
+    <t>#measurement.assignment</t>
+  </si>
+  <si>
+    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd-13C0</t>
+  </si>
+  <si>
+    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd-13C1</t>
+  </si>
+  <si>
+    <t>#measurement.compound</t>
+  </si>
+  <si>
+    <t>Compound</t>
+  </si>
+  <si>
+    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd</t>
+  </si>
+  <si>
+    <t>#measurement.formula</t>
+  </si>
+  <si>
+    <t>Mol_Formula</t>
+  </si>
+  <si>
+    <t>C5H8O4</t>
+  </si>
+  <si>
+    <t>C_isomers</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>#protocol.id</t>
   </si>
   <si>
+    <t>ICMS1</t>
+  </si>
+  <si>
+    <t>#.sample.id</t>
+  </si>
+  <si>
+    <t>SamplID</t>
+  </si>
+  <si>
+    <t>01_A0_Colon_T03-2017_naive_170427_UKy_GCB_rep1-quench</t>
+  </si>
+  <si>
+    <t>#measurement.isotopologue;#%type="13C"</t>
+  </si>
+  <si>
+    <t>13C0</t>
+  </si>
+  <si>
+    <t>13C1</t>
+  </si>
+  <si>
     <t>#.type</t>
   </si>
   <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>#measurement.raw_intensity;#%type="spectrometer peak area"</t>
+  </si>
+  <si>
+    <t>Intensity</t>
+  </si>
+  <si>
+    <t>7989221.83386388</t>
+  </si>
+  <si>
+    <t>289287.733437356</t>
+  </si>
+  <si>
     <t>#.instrument</t>
   </si>
   <si>
+    <t>Orbitrap Fusion</t>
+  </si>
+  <si>
+    <t>#measurement.corrected_raw_intensity;#%type="natural abundance corrected peak area"</t>
+  </si>
+  <si>
+    <t>Renormalized</t>
+  </si>
+  <si>
+    <t>8447352.89211</t>
+  </si>
+  <si>
     <t>#.ion_mode</t>
   </si>
   <si>
+    <t>NEGATIVE</t>
+  </si>
+  <si>
+    <t>Total.NA.Removed</t>
+  </si>
+  <si>
+    <t>8490014.36501</t>
+  </si>
+  <si>
     <t>#.ionization</t>
   </si>
   <si>
+    <t>ESI</t>
+  </si>
+  <si>
+    <t>Corrected</t>
+  </si>
+  <si>
     <t>#.instrument_type</t>
   </si>
   <si>
+    <t>IC-FTMS</t>
+  </si>
+  <si>
+    <t>Predicted</t>
+  </si>
+  <si>
+    <t>7839899.28802</t>
+  </si>
+  <si>
+    <t>439597.552377</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
     <t>#.description</t>
-  </si>
-  <si>
-    <t>#.chromatography_instrument_name</t>
-  </si>
-  <si>
-    <t>#.chromatography_type</t>
-  </si>
-  <si>
-    <t>#.column_name</t>
-  </si>
-  <si>
-    <t>#.chromatography_description</t>
-  </si>
-  <si>
-    <t>ICMS1</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Orbitrap Fusion</t>
-  </si>
-  <si>
-    <t>NEGATIVE</t>
-  </si>
-  <si>
-    <t>ESI</t>
-  </si>
-  <si>
-    <t>IC-FTMS</t>
   </si>
   <si>
     <t>ICMS Analytical Experiment with detection of compounds by comparison to standards. 
 Thermo RAW files are loaded into TraceFinder and peaks are manually curated. The area under the chromatograms is then exported to an Excel file. The area is then corrected for natural abundance. The natural abundance corrected area is then used to calculate the concentration of each compound for each sample. This calculation is done using standards. The first sample ran on the ICMS is a standard that has known concentrations of certain compounds. Then a number of samples are ran (typically 3-4) followed by another standard. The equation to calculate the concentration is "intensity in sample"/("intensity in first standard" + (("intensity in second standard" - "intensity in first standard")/# of samples) * "known concentration in standard", where the "intensity" is the aforementioned natural abundance corrected area, and the unlabeled intensity from the standard is used for all isotopologues of the compound. The reconstitution volume is simply the volume that the polar part of the sample was reconstituted to before going into the ICMS. The injection volume is how much of the reconstitution volume was injected into the ICMS. The protein is how much protein was in the entire sample (not only the small portion that was aliquoted for the ICMS). The polar split ratio is the fraction of the polar part of the sample that was aliquoted for the ICMS. This is calculated by dividing the weight of the polar aliquot for ICMS by the total weight of the polar portion of the sample. The protein normalized concentration is calculated using the equation, concentration * (reconstitution volume / 1000 / polar split ratio / protein).</t>
   </si>
   <si>
+    <t>Quantified_uM_ratio</t>
+  </si>
+  <si>
+    <t>#.chromatography_instrument_name</t>
+  </si>
+  <si>
     <t>Thermo Dionex ICS-5000+</t>
   </si>
   <si>
+    <t>#measurement.concentration;#%units=uM;#%type="calculated from standard"</t>
+  </si>
+  <si>
+    <t>Quantified_uM_sequence_ratio</t>
+  </si>
+  <si>
+    <t>#.chromatography_type</t>
+  </si>
+  <si>
     <t>Targeted IC</t>
   </si>
   <si>
+    <t>reconstitution_volume_uL</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>#.column_name</t>
+  </si>
+  <si>
     <t>Dionex IonPac AS11-HC-4um 2 mm i.d. x 250 mm</t>
   </si>
   <si>
+    <t>injection_volume_uL</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>#.chromatography_description</t>
+  </si>
+  <si>
+    <t>protein_mg</t>
+  </si>
+  <si>
+    <t>0.618176844244679</t>
+  </si>
+  <si>
+    <t>#.parent_id</t>
+  </si>
+  <si>
     <t>IC-FTMS_measurement</t>
   </si>
   <si>
-    <t>#ignore</t>
-  </si>
-  <si>
-    <t>Compound</t>
-  </si>
-  <si>
-    <t>Mol_Formula</t>
-  </si>
-  <si>
-    <t>C_isomers</t>
-  </si>
-  <si>
-    <t>SamplID</t>
-  </si>
-  <si>
-    <t>Intensity</t>
-  </si>
-  <si>
-    <t>Renormalized</t>
-  </si>
-  <si>
-    <t>Total.NA.Removed</t>
-  </si>
-  <si>
-    <t>Corrected</t>
-  </si>
-  <si>
-    <t>Predicted</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Quantified_uM_ratio</t>
-  </si>
-  <si>
-    <t>Quantified_uM_sequence_ratio</t>
-  </si>
-  <si>
-    <t>reconstitution_volume_uL</t>
-  </si>
-  <si>
-    <t>injection_volume_uL</t>
-  </si>
-  <si>
-    <t>protein_mg</t>
-  </si>
-  <si>
     <t>icms_split_ratio</t>
   </si>
   <si>
+    <t>0.255757329816374</t>
+  </si>
+  <si>
     <t>Amount_ProteinAdj_uMol_g_protein_RatioBased</t>
   </si>
   <si>
+    <t>#measurement.normalized_concentration;#%type="protein normalized";#%units="uMol/g"</t>
+  </si>
+  <si>
     <t>Amount_ProteinAdj_uMol_g_protein_SequenceBased</t>
   </si>
   <si>
     <t>CommentQuantification</t>
   </si>
   <si>
-    <t>#measurement.id</t>
-  </si>
-  <si>
-    <t>#measurement.assignment</t>
-  </si>
-  <si>
-    <t>#measurement.compound</t>
-  </si>
-  <si>
-    <t>#measurement.formula</t>
-  </si>
-  <si>
-    <t>#measurement.isotopologue;#%type="13C"</t>
-  </si>
-  <si>
-    <t>#measurement.raw_intensity;#%type="spectrometer peak area"</t>
-  </si>
-  <si>
-    <t>#measurement.corrected_raw_intensity;#%type="natural abundance corrected peak area"</t>
-  </si>
-  <si>
-    <t>#measurement.concentration;#%units=uM;#%type="calculated from standard"</t>
-  </si>
-  <si>
-    <t>#measurement.normalized_concentration;#%type="protein normalized";#%units="uMol/g"</t>
+    <t>Legend</t>
+  </si>
+  <si>
+    <t>Compound: name of assigned metabolite, noStd means assigment was NOT verified with standard compound</t>
   </si>
   <si>
     <t>#measurement.intensity;#%type="natural abundance corrected and protein normalized peak area";#%units="area/g"</t>
   </si>
   <si>
-    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd-13C0-01_A0_Colon_T03-2017_naive_170427_UKy_GCB_rep1-quench</t>
-  </si>
-  <si>
-    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd-13C0</t>
-  </si>
-  <si>
-    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd</t>
-  </si>
-  <si>
-    <t>C5H8O4</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>01_A0_Colon_T03-2017_naive_170427_UKy_GCB_rep1-quench</t>
-  </si>
-  <si>
-    <t>13C0</t>
-  </si>
-  <si>
-    <t>7989221.83386388</t>
-  </si>
-  <si>
-    <t>8447352.89211</t>
-  </si>
-  <si>
-    <t>8490014.36501</t>
-  </si>
-  <si>
-    <t>7839899.28802</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>0.618176844244679</t>
-  </si>
-  <si>
-    <t>0.255757329816374</t>
-  </si>
-  <si>
-    <t>Legend</t>
-  </si>
-  <si>
     <t>13664945.509939667</t>
   </si>
   <si>
-    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd-13C1-01_A0_Colon_T03-2017_naive_170427_UKy_GCB_rep1-quench</t>
-  </si>
-  <si>
-    <t>(S)-2-Acetolactate_Glutaric acid_Methylsuccinic acid_MP_NoStd-13C1</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>13C1</t>
-  </si>
-  <si>
-    <t>289287.733437356</t>
-  </si>
-  <si>
-    <t>439597.552377</t>
-  </si>
-  <si>
-    <t>Compound: name of assigned metabolite, noStd means assigment was NOT verified with standard compound</t>
-  </si>
-  <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>#.sample.id</t>
-  </si>
-  <si>
     <t>#.protocol.id=ICMS1</t>
-  </si>
-  <si>
-    <t>#.parent_id</t>
   </si>
 </sst>
 </file>
@@ -319,9 +319,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -359,7 +359,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -393,6 +393,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -427,9 +428,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -603,7 +605,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -611,140 +613,78 @@
         <v>0</v>
       </c>
       <c r="I1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L1" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="M1" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="N1" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="O1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="P1" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="R1" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="S1" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="T1" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="U1" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="V1" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="W1" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="I2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="N2" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="O2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="P2" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="S2" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="T2" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="U2" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="V2" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="W2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" t="s">
-        <v>30</v>
-      </c>
-      <c r="O4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>33</v>
-      </c>
-      <c r="R4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" t="s">
-        <v>35</v>
-      </c>
-      <c r="T4" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" t="s">
-        <v>37</v>
-      </c>
-      <c r="V4" t="s">
-        <v>38</v>
-      </c>
-      <c r="W4" t="s">
-        <v>39</v>
-      </c>
-      <c r="X4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
@@ -752,238 +692,238 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="I5" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="L5" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="M5" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="S5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Y5" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AA5" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="AB5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
-        <v>54</v>
+      <c r="A6" t="s">
+        <v>1</v>
       </c>
       <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" t="s">
+        <v>38</v>
+      </c>
+      <c r="O6" t="s">
+        <v>42</v>
+      </c>
+      <c r="P6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>48</v>
+      </c>
+      <c r="R6" t="s">
+        <v>51</v>
+      </c>
+      <c r="S6" t="s">
         <v>55</v>
       </c>
-      <c r="G6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="T6" t="s">
         <v>58</v>
       </c>
-      <c r="J6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" t="s">
-        <v>60</v>
-      </c>
-      <c r="M6" t="s">
-        <v>61</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="U6" t="s">
         <v>62</v>
       </c>
-      <c r="O6" t="s">
-        <v>61</v>
-      </c>
-      <c r="P6" t="s">
-        <v>63</v>
-      </c>
-      <c r="R6" t="s">
-        <v>57</v>
-      </c>
-      <c r="S6" t="s">
-        <v>57</v>
-      </c>
-      <c r="T6" t="s">
-        <v>64</v>
-      </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>65</v>
       </c>
-      <c r="V6" t="s">
-        <v>66</v>
-      </c>
       <c r="W6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X6" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Y6" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="Z6" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="N7" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="O7" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="P7" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="R7" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="S7" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="T7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="U7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V7" t="s">
         <v>66</v>
       </c>
       <c r="W7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="X7" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" t="s">
+        <v>30</v>
+      </c>
+      <c r="M8" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O8" t="s">
+        <v>15</v>
+      </c>
+      <c r="P8" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" t="s">
+        <v>15</v>
+      </c>
+      <c r="S8" t="s">
+        <v>15</v>
+      </c>
+      <c r="T8" t="s">
+        <v>59</v>
+      </c>
+      <c r="U8" t="s">
+        <v>63</v>
+      </c>
+      <c r="V8" t="s">
+        <v>66</v>
+      </c>
+      <c r="W8" t="s">
+        <v>70</v>
+      </c>
+      <c r="X8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z8" t="s">
         <v>76</v>
       </c>
-      <c r="AA7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M9" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" t="s">
-        <v>30</v>
-      </c>
-      <c r="O9" t="s">
-        <v>31</v>
-      </c>
-      <c r="P9" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>33</v>
-      </c>
-      <c r="R9" t="s">
-        <v>34</v>
-      </c>
-      <c r="S9" t="s">
-        <v>35</v>
-      </c>
-      <c r="T9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U9" t="s">
-        <v>37</v>
-      </c>
-      <c r="V9" t="s">
-        <v>38</v>
-      </c>
-      <c r="W9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X9" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>42</v>
+      <c r="AA8" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
@@ -991,176 +931,238 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="I10" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="K10" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="M10" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="S10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Y10" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="AC10" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="AD10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="D11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" t="s">
-        <v>54</v>
+      <c r="A11" t="s">
+        <v>1</v>
       </c>
       <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L11" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" t="s">
+        <v>34</v>
+      </c>
+      <c r="N11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O11" t="s">
+        <v>42</v>
+      </c>
+      <c r="P11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>48</v>
+      </c>
+      <c r="R11" t="s">
+        <v>51</v>
+      </c>
+      <c r="S11" t="s">
         <v>55</v>
       </c>
-      <c r="G11" t="s">
-        <v>56</v>
-      </c>
-      <c r="H11" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="T11" t="s">
         <v>58</v>
       </c>
-      <c r="K11" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M11" t="s">
-        <v>61</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="U11" t="s">
         <v>62</v>
       </c>
-      <c r="O11" t="s">
-        <v>61</v>
-      </c>
-      <c r="P11" t="s">
-        <v>63</v>
-      </c>
-      <c r="R11" t="s">
-        <v>57</v>
-      </c>
-      <c r="S11" t="s">
-        <v>57</v>
-      </c>
-      <c r="T11" t="s">
-        <v>64</v>
-      </c>
-      <c r="U11" t="s">
+      <c r="V11" t="s">
         <v>65</v>
       </c>
-      <c r="V11" t="s">
-        <v>66</v>
-      </c>
       <c r="W11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="X11" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Y11" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="Z11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AC11" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="L12" t="s">
-        <v>74</v>
+        <v>29</v>
       </c>
       <c r="M12" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="N12" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="O12" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="P12" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="R12" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="S12" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="T12" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="U12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="V12" t="s">
         <v>66</v>
       </c>
       <c r="W12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="X12" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="Y12" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="Z12" t="s">
+        <v>75</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" t="s">
+        <v>15</v>
+      </c>
+      <c r="P13" t="s">
+        <v>47</v>
+      </c>
+      <c r="R13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S13" t="s">
+        <v>15</v>
+      </c>
+      <c r="T13" t="s">
+        <v>59</v>
+      </c>
+      <c r="U13" t="s">
+        <v>63</v>
+      </c>
+      <c r="V13" t="s">
+        <v>66</v>
+      </c>
+      <c r="W13" t="s">
+        <v>70</v>
+      </c>
+      <c r="X13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z13" t="s">
         <v>76</v>
       </c>
-      <c r="AC12" t="s">
-        <v>77</v>
+      <c r="AC13" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
